--- a/data/rules/lookupTables.xlsx
+++ b/data/rules/lookupTables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hajibashi.Saba\Desktop\python-components\data\rules\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1AD97D-BFC8-4BD0-99F7-A28C133032C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77A60FD-3653-4A7F-BAD6-D180A4ACF473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="820" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aliases.AliasType" sheetId="1" r:id="rId1"/>
